--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -3169,7 +3169,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OKVED_J_SobAkc_23</t>
+          <t>OKVED_J_NetPr_23</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SobAkc_23</t>
+          <t>NetPr_23</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3279,7 +3279,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>OKVED_63_SobAkc_23</t>
+          <t>OKVED_63_NetPr_23</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SobAkc_23</t>
+          <t>NetPr_23</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
